--- a/excel_test.xlsx
+++ b/excel_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Докс\VCS7-U\TEST\TEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{81396F6E-DE51-44AD-9A99-B74A0C3892CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD74F29-0FAB-4ACC-AC53-66B18C94A414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32625" yWindow="540" windowWidth="20640" windowHeight="11835" xr2:uid="{96864389-8FC7-4F6E-8985-284C36C2FB18}"/>
   </bookViews>
@@ -33,12 +33,60 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="12">
+  <si>
+    <t>Эксель</t>
+  </si>
+  <si>
+    <t>Тут ещё текст</t>
+  </si>
+  <si>
+    <t>Это заполнение</t>
+  </si>
+  <si>
+    <t>Тест 1</t>
+  </si>
+  <si>
+    <t>Тест 2</t>
+  </si>
+  <si>
+    <t>Тест 3</t>
+  </si>
+  <si>
+    <t>Тест 4</t>
+  </si>
+  <si>
+    <t>Тест 5</t>
+  </si>
+  <si>
+    <t>Тест 6</t>
+  </si>
+  <si>
+    <t>Тест 7</t>
+  </si>
+  <si>
+    <t>Тест 8</t>
+  </si>
+  <si>
+    <t>Тест 9</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -381,9 +429,95 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F97C671-C32A-47EF-B594-B34CE1385844}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/excel_test.xlsx
+++ b/excel_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Докс\VCS7-U\TEST\TEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD74F29-0FAB-4ACC-AC53-66B18C94A414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD548D3-6FDE-4576-80F3-C228BC48220B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32625" yWindow="540" windowWidth="20640" windowHeight="11835" xr2:uid="{96864389-8FC7-4F6E-8985-284C36C2FB18}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="12">
   <si>
     <t>Эксель</t>
   </si>
@@ -42,9 +42,6 @@
     <t>Тут ещё текст</t>
   </si>
   <si>
-    <t>Это заполнение</t>
-  </si>
-  <si>
     <t>Тест 1</t>
   </si>
   <si>
@@ -70,6 +67,9 @@
   </si>
   <si>
     <t>Тест 9</t>
+  </si>
+  <si>
+    <t>Это заполнение и редактирование</t>
   </si>
 </sst>
 </file>
@@ -444,76 +444,103 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
         <v>3</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>4</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>5</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>6</v>
       </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
       <c r="F9" t="s">
+        <v>2</v>
+      </c>
+      <c r="G9" t="s">
         <v>8</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>9</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>10</v>
-      </c>
-      <c r="I9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="F10" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="F11" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="F12" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="F13" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
